--- a/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_64922_completo.xlsx
+++ b/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_64922_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re352e84898324309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R02b049d4980840ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,51 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2499</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_64922_completo.xlsx
+++ b/13156_Cuenca_Caplina/_raw_reportes_xlsx/IDConfig_64922_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R02b049d4980840ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R666d168ab86a4a04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,816 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6438</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6542</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6659</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7614</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8101</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7969</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9297</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>17/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2499</x:v>
+        <x:v>      0.9055</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2866</x:v>
+        <x:v>      0.8879</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2743</x:v>
+        <x:v>      0.8753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2887</x:v>
+        <x:v>      0.8876</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2988</x:v>
+        <x:v>      0.8968</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3156</x:v>
+        <x:v>      0.9019</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3206</x:v>
+        <x:v>      0.9129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3130</x:v>
+        <x:v>      0.9055</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3008</x:v>
+        <x:v>      0.8965</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2863</x:v>
+        <x:v>      0.8858</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2645</x:v>
+        <x:v>      0.8646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2526</x:v>
+        <x:v>      0.8629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2173</x:v>
+        <x:v>      0.8335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2173</x:v>
+        <x:v>      0.8284</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2360</x:v>
+        <x:v>      0.8455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2452</x:v>
+        <x:v>      0.8557</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2549</x:v>
+        <x:v>      0.8611</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2428</x:v>
+        <x:v>      0.8490</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2057</x:v>
+        <x:v>      0.8268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.1943</x:v>
+        <x:v>      0.8167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2035</x:v>
+        <x:v>      0.8235</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2128</x:v>
+        <x:v>      0.8269</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2196</x:v>
+        <x:v>      0.8318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2220</x:v>
+        <x:v>      0.8370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2220</x:v>
+        <x:v>      0.8353</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2339</x:v>
+        <x:v>      0.8457</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2267</x:v>
+        <x:v>      0.8404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2197</x:v>
+        <x:v>      0.8336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2104</x:v>
+        <x:v>      0.8285</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2150</x:v>
+        <x:v>      0.8336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2220</x:v>
+        <x:v>      0.8352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2548</x:v>
+        <x:v>      0.8628</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2429</x:v>
+        <x:v>      0.8472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2313</x:v>
+        <x:v>      0.8438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2453</x:v>
+        <x:v>      0.8541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2454</x:v>
+        <x:v>      0.8524</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2410</x:v>
+        <x:v>      0.8474</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2313</x:v>
+        <x:v>      0.8455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2360</x:v>
+        <x:v>      0.8490</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2337</x:v>
+        <x:v>      0.8455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2383</x:v>
+        <x:v>      0.8472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2384</x:v>
+        <x:v>      0.8490</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2383</x:v>
+        <x:v>      0.8472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2550</x:v>
+        <x:v>      0.8595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2550</x:v>
+        <x:v>      0.8664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2574</x:v>
+        <x:v>      0.8629</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2476</x:v>
+        <x:v>      0.8557</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2477</x:v>
+        <x:v>      0.8541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2526</x:v>
+        <x:v>      0.8610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2430</x:v>
+        <x:v>      0.8540</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2573</x:v>
+        <x:v>      0.8610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2597</x:v>
+        <x:v>      0.8681</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2384</x:v>
+        <x:v>      0.8438</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2293</x:v>
+        <x:v>      0.8406</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2338</x:v>
+        <x:v>      0.8455</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2034</x:v>
+        <x:v>      0.8285</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2220</x:v>
+        <x:v>      0.8336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2150</x:v>
+        <x:v>      0.8318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.1085</x:v>
+        <x:v>      0.7526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0469</x:v>
+        <x:v>      0.8235</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0550</x:v>
+        <x:v>      0.8371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0614</x:v>
+        <x:v>      0.8336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0634</x:v>
+        <x:v>      0.8353</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0675</x:v>
+        <x:v>      0.8387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0779</x:v>
+        <x:v>      0.8472</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0697</x:v>
+        <x:v>      0.8404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,1317 +2064,1332 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.8217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8438</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8301</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8405</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9116</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1314</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1362</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1629</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1726</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2356</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3215</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7626</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8601</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2973</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1944</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1286</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0571</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      1.0448</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0489</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0408</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0634</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0675</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0758</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0409</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0429</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0571</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0572</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0551</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0614</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0593</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0550</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0720</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0616</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0552</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0697</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0592</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9729</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9129</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9111</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9111</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9149</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9111</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9074</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9222</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9332</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9222</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0144</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0914</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0960</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1314</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1362</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1340</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1481</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1389</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1681</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1753</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1654</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1339</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1413</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1629</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1726</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2028</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2181</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2562</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2640</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2381</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2304</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2356</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2555</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2564</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2433</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.3690</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4217</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4464</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.3215</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.3470</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7626</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6238</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2862</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5739</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9663</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.2609</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8756</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0706</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5703</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.8601</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0372</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.9737</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1698</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4182</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.2973</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1944</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.1286</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0780</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0910</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0571</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0320</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0228</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0213</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.0448</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>15/03/2026</x:t>
         </x:is>
       </x:c>
@@ -2605,6 +3430,21 @@
       </x:c>
       <x:c s="3">
         <x:v>      1.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0832</x:v>
       </x:c>
     </x:row>
     <x:row>
